--- a/MM/11analitik_31/11analitik.xlsx
+++ b/MM/11analitik_31/11analitik.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mADEMatik\Desktop\GEO12\MM\11analitik_31\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B80F3E9-445B-4927-B1B1-0B924D61DED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0854E18F-37FF-4569-91A5-16790213DABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
     <t>Başarı Puanı</t>
   </si>
   <si>
-    <t>Görüşler ve Öneriler</t>
-  </si>
-  <si>
     <t>Önemli Eksikleri Var (1)</t>
   </si>
   <si>
@@ -154,10 +151,13 @@
     <t>Küçük hatalar var.</t>
   </si>
   <si>
-    <t>TOPLAM</t>
-  </si>
-  <si>
     <t>1. TEMA - NİCELİKLER VE DEĞİŞİMLER (1) - ANALİTİK DERECELİ PUANLAMA ANAHTARI 1.1</t>
+  </si>
+  <si>
+    <t>TOPLAM PUAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Bu form, öğrencinin performans görevini değerlendirmeniz amacıyla hazırlanmıştır. Öğrencinin belirtilen ölçütleri öğrenme durumunu en doğru yansıtan başarı düzeyini puanlayınız.</t>
   </si>
 </sst>
 </file>
@@ -191,7 +191,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -259,6 +259,19 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -277,9 +290,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -337,14 +347,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,306 +696,298 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H19"/>
+  <dimension ref="B1:G18"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" style="11" customWidth="1"/>
     <col min="4" max="6" width="22.44140625" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.21875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.21875" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+    </row>
+    <row r="6" spans="2:7" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="25"/>
+    </row>
+    <row r="8" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="26"/>
-    </row>
-    <row r="7" spans="2:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="19"/>
-      <c r="C8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="F10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="E11" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="14" t="s">
+      <c r="F15" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="E16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="C17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="2:8" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="15" t="s">
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="2:7" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="C3:H3"/>
+  <mergeCells count="9">
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.55118110236220474" bottom="0.55118110236220474" header="0" footer="0"/>
